--- a/design/tables/UiPrefab.xlsx
+++ b/design/tables/UiPrefab.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UiPrefab" sheetId="1" r:id="R3571f0431d784e9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UiPrefab" sheetId="1" r:id="R4b3b9eaded294440"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -582,6 +582,17 @@
         <x:v>ui/gm</x:v>
       </x:c>
     </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>guide_hint</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>ui/guide_hint</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/UiPrefab.xlsx
+++ b/design/tables/UiPrefab.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UiPrefab" sheetId="1" r:id="R4b3b9eaded294440"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UiPrefab" sheetId="1" r:id="R52687ac1380c4a9a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -593,6 +593,17 @@
         <x:v>ui/guide_hint</x:v>
       </x:c>
     </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>evolution_card</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>ui/evolution_card</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/UiPrefab.xlsx
+++ b/design/tables/UiPrefab.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UiPrefab" sheetId="1" r:id="R52687ac1380c4a9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UiPrefab" sheetId="1" r:id="R811ce97e0a604bcb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -604,6 +604,50 @@
         <x:v>ui/evolution_card</x:v>
       </x:c>
     </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>loadout</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>ui/loadout</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>loadout_card</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>ui/loadout_card</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>wave_preview</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>ui/wave_preview</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>enemy_preview_card</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>ui/enemy_preview_card</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/UiPrefab.xlsx
+++ b/design/tables/UiPrefab.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UiPrefab" sheetId="1" r:id="R811ce97e0a604bcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UiPrefab" sheetId="1" r:id="Rbab221ff4aa74760"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -648,6 +648,28 @@
         <x:v>ui/enemy_preview_card</x:v>
       </x:c>
     </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>challenge_pick</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>ui/challenge_pick</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>challenge_card</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>ui/challenge_card</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/UiPrefab.xlsx
+++ b/design/tables/UiPrefab.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UiPrefab" sheetId="1" r:id="Rbab221ff4aa74760"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UiPrefab" sheetId="1" r:id="R084111e6de3a4385"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -670,6 +670,39 @@
         <x:v>ui/challenge_card</x:v>
       </x:c>
     </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>challenge_loadout</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>ui/challenge_loadout</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>challenge_staff_card</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>ui/challenge_staff_card</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="28" customHeight="1">
+      <x:c r="A38" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>loading</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>ui/loading</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/UiPrefab.xlsx
+++ b/design/tables/UiPrefab.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UiPrefab" sheetId="1" r:id="R084111e6de3a4385"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UiPrefab" sheetId="1" r:id="R2b08d65f48344a78"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -703,6 +703,17 @@
         <x:v>ui/loading</x:v>
       </x:c>
     </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>shop</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>ui/shop</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/UiPrefab.xlsx
+++ b/design/tables/UiPrefab.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UiPrefab" sheetId="1" r:id="R2b08d65f48344a78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UiPrefab" sheetId="1" r:id="R487bd17fcad84e4d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -714,6 +714,17 @@
         <x:v>ui/shop</x:v>
       </x:c>
     </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>challenge_topics</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>ui/challenge_topics</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/UiPrefab.xlsx
+++ b/design/tables/UiPrefab.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UiPrefab" sheetId="1" r:id="R487bd17fcad84e4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UiPrefab" sheetId="1" r:id="Ra113328abc214635"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -725,6 +725,17 @@
         <x:v>ui/challenge_topics</x:v>
       </x:c>
     </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>ranking</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>ui/ranking</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/UiPrefab.xlsx
+++ b/design/tables/UiPrefab.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UiPrefab" sheetId="1" r:id="Ra113328abc214635"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UiPrefab" sheetId="1" r:id="Rb5ec6805933646fa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -736,6 +736,17 @@
         <x:v>ui/ranking</x:v>
       </x:c>
     </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="7" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B42" s="2" t="str">
+        <x:v>technology</x:v>
+      </x:c>
+      <x:c r="C42" s="2" t="str">
+        <x:v>ui/technology</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
